--- a/file/bz-100.xlsx
+++ b/file/bz-100.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,1350 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>601002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>晋亿实业</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>601311</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>骆驼股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>603230</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>内蒙新华</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>603163</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>圣晖集成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>002138</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>顺络电子</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>603650</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>彤程新材</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>605058</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>澳弘电子</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>603095</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>越剑智能</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>002056</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>横店东磁</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>603203</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>快克智能</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>603328</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>依顿电子</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>603025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>大豪科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>603588</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>高能环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>002003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>伟星股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>002545</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>东方铁塔</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>600710</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>苏美达</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>002706</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>良信股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>002270</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>华明装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>603132</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>金徽股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>601168</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>西部矿业</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>600531</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>豫光金铅</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>000672</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>上峰水泥</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>600757</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>长江传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>002632</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>道明光学</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>603788</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>宁波高发</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>603087</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>甘李药业</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>603111</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>康尼机电</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>001299</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>601211</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>国泰海通</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>600030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>002705</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>新宝股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>605580</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>恒盛能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>603332</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>苏州龙杰</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>600000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>浦发银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>002972</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>科安达</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>000726</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>鲁  泰Ａ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>603519</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>立霸股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>603115</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>海星股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>000404</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>长虹华意</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>601216</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>君正集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>002884</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>凌霄泵业</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>002479</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>富春环保</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>605066</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>天正电气</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>600742</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>一汽富维</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>002318</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>久立特材</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>603075</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>热威股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>002236</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>大华股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>601061</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>中信金属</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>000719</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>中原传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>001216</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>华瓷股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>002091</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>江苏国泰</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>000156</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>华数传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>603298</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>杭叉集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>600874</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>创业环保</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>002303</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>美盈森</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>000537</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>中绿电</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>002597</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>金禾实业</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>600064</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>南京高科</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>600210</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>紫江企业</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>000878</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>云南铜业</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>600908</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>无锡银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>601688</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>华泰证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>600020</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>中原高速</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>603811</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>诚意药业</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>605268</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>002615</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>哈尔斯</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>600283</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>钱江水利</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>601665</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>齐鲁银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>600285</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>羚锐制药</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>002701</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>奥瑞金</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>002444</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>巨星科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>601126</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>四方股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>601766</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>中国中车</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>603309</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>维力医疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>600527</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>江南高纤</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>603218</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>日月股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>000728</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>国元证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>600219</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>南山铝业</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>000755</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>山西高速</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>000630</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>铜陵有色</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>002532</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>天山铝业</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>002083</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>孚日股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>603080</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>新疆火炬</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>600901</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>江苏金租</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>001206</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>依依股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>600897</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>厦门空港</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>601919</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>中远海控</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>600526</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>菲达环保</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>001227</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>兰州银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>601138</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>工业富联</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>600681</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>百川能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>600098</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>广州发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>000776</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>广发证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>600496</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>精工钢构</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>600369</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>西南证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>000027</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>深圳能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>002352</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>顺丰控股</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>603816</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>顾家家居</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>601555</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>东吴证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>600875</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>东方电气</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>002588</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>史丹利</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>002215</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>诺 普 信</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>002061</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>浙江交科</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>605169</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>洪通燃气</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>002533</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>金杯电工</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>601083</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>锦江航运</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>002027</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>分众传媒</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>601619</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>嘉泽新能</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>601330</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>绿色动力</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>605077</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>华康股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>603566</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>普莱柯</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>002404</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>嘉欣丝绸</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
